--- a/BKQBF_TAB-5.xlsx
+++ b/BKQBF_TAB-5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{BC93C416-C7D8-4083-8F6A-97B4473368CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85BE19C2-EB3B-4047-A157-9CC2138FCB4E}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{BC93C416-C7D8-4083-8F6A-97B4473368CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AC5F422-6D7E-4127-824E-DEFACD2D5EF6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{53633E7E-D6F2-4DB1-8EFC-B5ACF3C598DF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="192">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -552,6 +552,66 @@
   </si>
   <si>
     <t>CARNE HB CONG BKC CX COM 18,7 KG</t>
+  </si>
+  <si>
+    <t>BISCOITO BISCOFF CX C 300UND</t>
+  </si>
+  <si>
+    <t>CARNE FRALDINHA DESF DEFUMADA CX 4KG 4X1</t>
+  </si>
+  <si>
+    <t>COOKIE GRANULADO BAUNI CL CX5X1KG</t>
+  </si>
+  <si>
+    <t>CRUMBS BISCOFF CX C 6KG 8X750G</t>
+  </si>
+  <si>
+    <t>ETIQUETA LACRE DE SEGURANCA DLV C/1000UN</t>
+  </si>
+  <si>
+    <t>PROTEINA SORO DE LEITE CX 12X0,8KG</t>
+  </si>
+  <si>
+    <t>COCA COLA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>COCA COLA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO LATA DLV BK</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>GUARANA DIET LATA</t>
+  </si>
+  <si>
+    <t>GUARANA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>GUARANA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>GUARANA ZERO LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>GUARANA ZERO LATA DLV BK</t>
+  </si>
+  <si>
+    <t>REFRIGERANTE GUARANA LATA</t>
+  </si>
+  <si>
+    <t>SPRITE LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>SPRITE LATA DLV BK</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB15583B-E240-453F-9C06-A311E2614116}">
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
@@ -3960,6 +4020,346 @@
         <v>1</v>
       </c>
     </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="4">
+        <v>41475</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C171" s="8">
+        <v>300</v>
+      </c>
+      <c r="D171" s="8">
+        <v>50</v>
+      </c>
+      <c r="E171" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="4">
+        <v>42049</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C172" s="8">
+        <v>4</v>
+      </c>
+      <c r="D172" s="8">
+        <v>1</v>
+      </c>
+      <c r="E172" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="4">
+        <v>39059</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C173" s="8">
+        <v>5</v>
+      </c>
+      <c r="D173" s="8">
+        <v>1</v>
+      </c>
+      <c r="E173" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="4">
+        <v>41476</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C174" s="8">
+        <v>6</v>
+      </c>
+      <c r="D174" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E174" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="4">
+        <v>37842</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C175" s="8">
+        <v>1000</v>
+      </c>
+      <c r="D175" s="9">
+        <v>0</v>
+      </c>
+      <c r="E175" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="4">
+        <v>40442</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C176" s="8">
+        <v>10.61</v>
+      </c>
+      <c r="D176" s="9">
+        <v>0</v>
+      </c>
+      <c r="E176" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="4">
+        <v>7210467</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C177" s="8">
+        <v>1</v>
+      </c>
+      <c r="D177" s="9">
+        <v>0</v>
+      </c>
+      <c r="E177" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="4">
+        <v>7210468</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C178" s="8">
+        <v>1</v>
+      </c>
+      <c r="D178" s="9">
+        <v>0</v>
+      </c>
+      <c r="E178" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="4">
+        <v>7210469</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C179" s="8">
+        <v>1</v>
+      </c>
+      <c r="D179" s="9">
+        <v>0</v>
+      </c>
+      <c r="E179" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="4">
+        <v>7210471</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C180" s="8">
+        <v>1</v>
+      </c>
+      <c r="D180" s="9">
+        <v>0</v>
+      </c>
+      <c r="E180" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="4">
+        <v>7210472</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C181" s="8">
+        <v>1</v>
+      </c>
+      <c r="D181" s="9">
+        <v>0</v>
+      </c>
+      <c r="E181" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="4">
+        <v>7210473</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C182" s="8">
+        <v>1</v>
+      </c>
+      <c r="D182" s="9">
+        <v>0</v>
+      </c>
+      <c r="E182" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="4">
+        <v>7210474</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C183" s="8">
+        <v>1</v>
+      </c>
+      <c r="D183" s="9">
+        <v>0</v>
+      </c>
+      <c r="E183" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="4">
+        <v>7210475</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C184" s="8">
+        <v>1</v>
+      </c>
+      <c r="D184" s="9">
+        <v>0</v>
+      </c>
+      <c r="E184" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="4">
+        <v>7210476</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C185" s="8">
+        <v>1</v>
+      </c>
+      <c r="D185" s="9">
+        <v>0</v>
+      </c>
+      <c r="E185" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="4">
+        <v>7210478</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C186" s="8">
+        <v>1</v>
+      </c>
+      <c r="D186" s="9">
+        <v>0</v>
+      </c>
+      <c r="E186" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="4">
+        <v>7210479</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C187" s="8">
+        <v>1</v>
+      </c>
+      <c r="D187" s="9">
+        <v>0</v>
+      </c>
+      <c r="E187" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="4">
+        <v>7210480</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C188" s="8">
+        <v>1</v>
+      </c>
+      <c r="D188" s="9">
+        <v>0</v>
+      </c>
+      <c r="E188" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="4">
+        <v>9013</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C189" s="8">
+        <v>1</v>
+      </c>
+      <c r="D189" s="9">
+        <v>0</v>
+      </c>
+      <c r="E189" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="4">
+        <v>9014</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C190" s="8">
+        <v>1</v>
+      </c>
+      <c r="D190" s="9">
+        <v>0</v>
+      </c>
+      <c r="E190" s="7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/BKQBF_TAB-5.xlsx
+++ b/BKQBF_TAB-5.xlsx
@@ -804,6 +804,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
